--- a/sheets/조재수대금교본/검수/가시버시 사랑.xlsx
+++ b/sheets/조재수대금교본/검수/가시버시 사랑.xlsx
@@ -5645,7 +5645,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -5720,8 +5720,7 @@
       <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㴌
-‹</t>
+㴌</t>
         </is>
       </c>
       <c r="M4" s="23"/>
@@ -5735,8 +5734,7 @@
       <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-㴌
-‹</t>
+㴌</t>
         </is>
       </c>
       <c r="Q4" s="23"/>
@@ -5752,7 +5750,7 @@
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-淋∽</t>
+淋</t>
         </is>
       </c>
       <c r="E5" s="24"/>
@@ -5793,7 +5791,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C6" s="22"/>
@@ -5829,7 +5827,7 @@
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰∧</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="O6" s="22"/>
@@ -5900,12 +5898,7 @@
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
@@ -5914,18 +5907,13 @@
         </is>
       </c>
       <c r="G8" s="24"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
       <c r="J8" s="21"/>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="M8" s="24"/>
@@ -5933,8 +5921,7 @@
       <c r="O8" s="24"/>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="Q8" s="24"/>
@@ -5955,7 +5942,7 @@
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="G9" s="22"/>
@@ -6157,53 +6144,21 @@
     </row>
     <row r="14" ht="90.2" customHeight="true">
       <c r="A14" s="0"/>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B14" s="21"/>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P14" s="21"/>
       <c r="Q14" s="24"/>
     </row>
     <row r="15" ht="6.0" customHeight="true">
@@ -6242,7 +6197,7 @@
       <c r="C17" s="22"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E17" s="22"/>
@@ -6278,7 +6233,7 @@
       <c r="O17" s="22"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="Q17" s="22"/>
@@ -6299,7 +6254,7 @@
       <c r="I18" s="23"/>
       <c r="J18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢⊏∼</t>
+          <t xml:space="preserve">潢∼</t>
         </is>
       </c>
       <c r="K18" s="23"/>
@@ -6338,11 +6293,7 @@
         </is>
       </c>
       <c r="I19" s="24"/>
-      <c r="J19" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J19" s="21"/>
       <c r="K19" s="24"/>
       <c r="L19" s="21" t="inlineStr">
         <is>
@@ -6415,8 +6366,7 @@
       <c r="E21" s="23"/>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-∧</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G21" s="23"/>
@@ -6459,23 +6409,18 @@
       <c r="C22" s="24"/>
       <c r="D22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="E22" s="24"/>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧·
+          <t xml:space="preserve">·
 △</t>
         </is>
       </c>
       <c r="G22" s="24"/>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H22" s="21"/>
       <c r="I22" s="24"/>
       <c r="J22" s="21" t="inlineStr">
         <is>
@@ -6495,8 +6440,7 @@
       <c r="O22" s="24"/>
       <c r="P22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="Q22" s="24"/>
@@ -6511,13 +6455,13 @@
       <c r="C23" s="22"/>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∧⊏∼</t>
+          <t xml:space="preserve">∼</t>
         </is>
       </c>
       <c r="G23" s="22"/>
@@ -6684,47 +6628,19 @@
         </is>
       </c>
       <c r="C28" s="24"/>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D28" s="21"/>
       <c r="E28" s="24"/>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F28" s="21"/>
       <c r="G28" s="24"/>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H28" s="21"/>
       <c r="I28" s="24"/>
-      <c r="J28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J28" s="21"/>
       <c r="K28" s="24"/>
-      <c r="L28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L28" s="21"/>
       <c r="M28" s="24"/>
-      <c r="N28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N28" s="21"/>
       <c r="O28" s="24"/>
-      <c r="P28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P28" s="21"/>
       <c r="Q28" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/가시버시 사랑.xlsx
+++ b/sheets/조재수대금교본/검수/가시버시 사랑.xlsx
@@ -5645,7 +5645,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -5750,7 +5750,7 @@
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-淋</t>
+淋∽</t>
         </is>
       </c>
       <c r="E5" s="24"/>
@@ -5791,7 +5791,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="C6" s="22"/>
@@ -5827,7 +5827,7 @@
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰∧</t>
         </is>
       </c>
       <c r="O6" s="22"/>
@@ -5898,7 +5898,11 @@
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
@@ -5942,7 +5946,7 @@
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="G9" s="22"/>
@@ -6197,7 +6201,7 @@
       <c r="C17" s="22"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="E17" s="22"/>
@@ -6233,7 +6237,7 @@
       <c r="O17" s="22"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="Q17" s="22"/>
@@ -6254,7 +6258,7 @@
       <c r="I18" s="23"/>
       <c r="J18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∼</t>
+          <t xml:space="preserve">潢⊏∼</t>
         </is>
       </c>
       <c r="K18" s="23"/>
@@ -6366,7 +6370,8 @@
       <c r="E21" s="23"/>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+∧</t>
         </is>
       </c>
       <c r="G21" s="23"/>
@@ -6415,7 +6420,7 @@
       <c r="E22" s="24"/>
       <c r="F22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">∧·
 △</t>
         </is>
       </c>
@@ -6455,13 +6460,13 @@
       <c r="C23" s="22"/>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳ㄱ</t>
         </is>
       </c>
       <c r="E23" s="22"/>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">∼</t>
+          <t xml:space="preserve">∧⊏∼</t>
         </is>
       </c>
       <c r="G23" s="22"/>

--- a/sheets/조재수대금교본/검수/가시버시 사랑.xlsx
+++ b/sheets/조재수대금교본/검수/가시버시 사랑.xlsx
@@ -5591,28 +5591,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="11.63" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="11.63" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="11.63" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="11.63" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="11.63" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="11.63" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="11.63" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="11.63" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60.61" customHeight="true">
+    <row r="2" ht="67.8" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="90.2" customHeight="true">
+    <row r="3" ht="100.96" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="90.2" customHeight="true">
+    <row r="4" ht="100.96" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="90.2" customHeight="true">
+    <row r="5" ht="100.96" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="90.2" customHeight="true">
+    <row r="6" ht="100.96" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="90.2" customHeight="true">
+    <row r="7" ht="100.96" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="90.2" customHeight="true">
+    <row r="8" ht="100.96" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="90.2" customHeight="true">
+    <row r="9" ht="100.96" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="90.2" customHeight="true">
+    <row r="10" ht="100.96" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="90.2" customHeight="true">
+    <row r="11" ht="100.96" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="90.2" customHeight="true">
+    <row r="12" ht="100.96" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="90.2" customHeight="true">
+    <row r="13" ht="100.96" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="90.2" customHeight="true">
+    <row r="14" ht="100.96" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -6168,7 +6168,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="60.61" customHeight="true">
+    <row r="16" ht="67.8" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
       <c r="P16" s="20"/>
       <c r="Q16" s="20"/>
     </row>
-    <row r="17" ht="90.2" customHeight="true">
+    <row r="17" ht="100.96" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="Q17" s="22"/>
     </row>
-    <row r="18" ht="90.2" customHeight="true">
+    <row r="18" ht="100.96" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -6273,7 +6273,7 @@
       <c r="P18" s="21"/>
       <c r="Q18" s="23"/>
     </row>
-    <row r="19" ht="90.2" customHeight="true">
+    <row r="19" ht="100.96" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="Q19" s="24"/>
     </row>
-    <row r="20" ht="90.2" customHeight="true">
+    <row r="20" ht="100.96" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
       <c r="P20" s="21"/>
       <c r="Q20" s="22"/>
     </row>
-    <row r="21" ht="90.2" customHeight="true">
+    <row r="21" ht="100.96" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="Q21" s="23"/>
     </row>
-    <row r="22" ht="90.2" customHeight="true">
+    <row r="22" ht="100.96" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="Q22" s="24"/>
     </row>
-    <row r="23" ht="90.2" customHeight="true">
+    <row r="23" ht="100.96" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
       </c>
       <c r="Q23" s="22"/>
     </row>
-    <row r="24" ht="90.2" customHeight="true">
+    <row r="24" ht="100.96" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="Q24" s="23"/>
     </row>
-    <row r="25" ht="90.2" customHeight="true">
+    <row r="25" ht="100.96" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="Q25" s="24"/>
     </row>
-    <row r="26" ht="90.2" customHeight="true">
+    <row r="26" ht="100.96" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="Q26" s="22"/>
     </row>
-    <row r="27" ht="90.2" customHeight="true">
+    <row r="27" ht="100.96" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -6625,7 +6625,7 @@
       <c r="P27" s="21"/>
       <c r="Q27" s="23"/>
     </row>
-    <row r="28" ht="90.2" customHeight="true">
+    <row r="28" ht="100.96" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="59"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
